--- a/resources/Clinicians.xlsx
+++ b/resources/Clinicians.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BaraaAlmousa\Documents\projects\clone project\sff-demo-1-enhance\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BaraaAlmousa\Documents\projects\clone project\sff-demo\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D9444-F51F-4B07-80DD-28F546B7766A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6706E95-CCE2-48DB-87C1-A8CB733FC51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{35E36AF3-8D1B-43CA-B917-B7603738086A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="581">
   <si>
     <t>Clinician License</t>
   </si>
@@ -347,21 +347,9 @@
     <t>Al Mu'tarid</t>
   </si>
   <si>
-    <t>GT38130</t>
-  </si>
-  <si>
-    <t>HAGER ELMUTASIM ELHASSAN MOHAMMED</t>
-  </si>
-  <si>
     <t>Manager of Pharmacy - Chief Pharmacist</t>
   </si>
   <si>
-    <t>IDEAL FUTURE PHARMACY - L.L.C.</t>
-  </si>
-  <si>
-    <t>PF5605</t>
-  </si>
-  <si>
     <t>GD46160</t>
   </si>
   <si>
@@ -470,18 +458,6 @@
     <t>12/08/2027</t>
   </si>
   <si>
-    <t>GT37991</t>
-  </si>
-  <si>
-    <t>AHINA ABUBAKER MUHAMMED SADIQ</t>
-  </si>
-  <si>
-    <t>JUST HEALTH PHARMACY</t>
-  </si>
-  <si>
-    <t>PF5101</t>
-  </si>
-  <si>
     <t>12/06/2025</t>
   </si>
   <si>
@@ -524,18 +500,6 @@
     <t>30/06/2027</t>
   </si>
   <si>
-    <t>GT38003</t>
-  </si>
-  <si>
-    <t>FAMNA ROOHI ROOHI NECHI KANDAN NECHI KANDAN</t>
-  </si>
-  <si>
-    <t>ASTER PHARMACIES GROUP L.L.C - BRANCH OF ABU DHABI 19</t>
-  </si>
-  <si>
-    <t>PF5484</t>
-  </si>
-  <si>
     <t>GT38004</t>
   </si>
   <si>
@@ -1041,6 +1005,780 @@
   </si>
   <si>
     <t>19/06/2027</t>
+  </si>
+  <si>
+    <t>GP10068</t>
+  </si>
+  <si>
+    <t>MAISA ABDIEN ISMAIL SAIED</t>
+  </si>
+  <si>
+    <t>14/07/2020</t>
+  </si>
+  <si>
+    <t>24/05/2027</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>GP10419</t>
+  </si>
+  <si>
+    <t>WAEL ALY ABDELMOATY MOHAMED</t>
+  </si>
+  <si>
+    <t>AL AMIR PHARMACY - SOLE PROPRIETORSHIP L.L.C.</t>
+  </si>
+  <si>
+    <t>PF1241</t>
+  </si>
+  <si>
+    <t>25/04/2004</t>
+  </si>
+  <si>
+    <t>PCR Provider</t>
+  </si>
+  <si>
+    <t>GP10439</t>
+  </si>
+  <si>
+    <t>AMAL MAHD RASHAD ABUALRUB</t>
+  </si>
+  <si>
+    <t>AL HAKEEM LAND PHARMACY - SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1274</t>
+  </si>
+  <si>
+    <t>12/03/2021</t>
+  </si>
+  <si>
+    <t>14/04/2027</t>
+  </si>
+  <si>
+    <t>GP10453</t>
+  </si>
+  <si>
+    <t>RAHEEMA SHAMS UDHEEN</t>
+  </si>
+  <si>
+    <t>ABDULLA PHARMACY - L.L.C</t>
+  </si>
+  <si>
+    <t>PF1280</t>
+  </si>
+  <si>
+    <t>Al Ain Industrial Area</t>
+  </si>
+  <si>
+    <t>14/05/2002</t>
+  </si>
+  <si>
+    <t>17/08/2027</t>
+  </si>
+  <si>
+    <t>GP10477</t>
+  </si>
+  <si>
+    <t>AREF MOHAMMED MOHAMMED ALQADASI</t>
+  </si>
+  <si>
+    <t>LOTUS  PHARMACY LLC</t>
+  </si>
+  <si>
+    <t>PF2608</t>
+  </si>
+  <si>
+    <t>12/08/2003</t>
+  </si>
+  <si>
+    <t>02/06/2027</t>
+  </si>
+  <si>
+    <t>GP10550</t>
+  </si>
+  <si>
+    <t>SHINE RAMAKRISHNAN RAMAKRISHNAN PADINJARE</t>
+  </si>
+  <si>
+    <t>Pharmacy Technician</t>
+  </si>
+  <si>
+    <t>SHEIKH SHAKHBOUT MEDICAL CITY OUTPATIENT PHARMACY- GROUND FLOOR</t>
+  </si>
+  <si>
+    <t>PF3221</t>
+  </si>
+  <si>
+    <t>25/04/2005</t>
+  </si>
+  <si>
+    <t>20/04/2027</t>
+  </si>
+  <si>
+    <t>GP10534</t>
+  </si>
+  <si>
+    <t>EMAN MHD RATEB MANLA</t>
+  </si>
+  <si>
+    <t>7D PHARMACY - SOLE PROPRIETORSGIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF5290</t>
+  </si>
+  <si>
+    <t>07/01/2021</t>
+  </si>
+  <si>
+    <t>24/03/2027</t>
+  </si>
+  <si>
+    <t>GP10607</t>
+  </si>
+  <si>
+    <t>THAIKATTIL JOSEPH JOHNSON</t>
+  </si>
+  <si>
+    <t>NMC Pharmacy  - LLC - O.P.C</t>
+  </si>
+  <si>
+    <t>PF1446</t>
+  </si>
+  <si>
+    <t>16/03/2021</t>
+  </si>
+  <si>
+    <t>GP10713</t>
+  </si>
+  <si>
+    <t>ABDUL MAJEED THAZHE PUTHIYOTTIL</t>
+  </si>
+  <si>
+    <t>29/05/2004</t>
+  </si>
+  <si>
+    <t>27/05/2027</t>
+  </si>
+  <si>
+    <t>GP10722</t>
+  </si>
+  <si>
+    <t>Abdulla Chithari Majeed CHITHARI Majeed</t>
+  </si>
+  <si>
+    <t>DAS MEDICAL CENTER PHARMACY</t>
+  </si>
+  <si>
+    <t>PF1316</t>
+  </si>
+  <si>
+    <t>14/10/2020</t>
+  </si>
+  <si>
+    <t>22/05/2027</t>
+  </si>
+  <si>
+    <t>GP10746</t>
+  </si>
+  <si>
+    <t>ASHRAF KOTTAMPARA</t>
+  </si>
+  <si>
+    <t>SHEIKH KHALIFA MEDICAL CITY PHARMACY - INPATIENT</t>
+  </si>
+  <si>
+    <t>PF1532</t>
+  </si>
+  <si>
+    <t>06/10/2004</t>
+  </si>
+  <si>
+    <t>GP10764</t>
+  </si>
+  <si>
+    <t>MOHAMED AFZAL ATHAMANAKATH</t>
+  </si>
+  <si>
+    <t>CLEVELAND CLINIC ABU DHABI PHARMACY LLC - SOLE PROPRIETORSHIP LLC</t>
+  </si>
+  <si>
+    <t>PF2761</t>
+  </si>
+  <si>
+    <t>03/02/2021</t>
+  </si>
+  <si>
+    <t>15/02/2027</t>
+  </si>
+  <si>
+    <t>GP10780</t>
+  </si>
+  <si>
+    <t>SUJEESH VALIYAPARAMBIL SURESHBABU</t>
+  </si>
+  <si>
+    <t>NOOR ALAHLI PHARMACY L.L.C. - BRANCH</t>
+  </si>
+  <si>
+    <t>PF3055</t>
+  </si>
+  <si>
+    <t>Baniyas</t>
+  </si>
+  <si>
+    <t>24/02/2021</t>
+  </si>
+  <si>
+    <t>17/03/2027</t>
+  </si>
+  <si>
+    <t>TA0076</t>
+  </si>
+  <si>
+    <t>Eiman Jawdat Saeed Asad</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>Pharmacist</t>
+  </si>
+  <si>
+    <t>ALTHIQA AL DOWALIAH PHARMACY L.L.C - SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1637</t>
+  </si>
+  <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>TA0749</t>
+  </si>
+  <si>
+    <t>MUNEERA KHAMIS SHAMBI ABDULRASOUL ALBLOOSHI</t>
+  </si>
+  <si>
+    <t>AIN AL KHALEEJ HOSPITAL IN PATIENT PHARMACY</t>
+  </si>
+  <si>
+    <t>PF2514</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>TA0799</t>
+  </si>
+  <si>
+    <t>RAHAF AHMED  MOHAMMED AHMED</t>
+  </si>
+  <si>
+    <t>PRIME CURE PHARMACY - SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1649</t>
+  </si>
+  <si>
+    <t>13/01/2026</t>
+  </si>
+  <si>
+    <t>TA0789</t>
+  </si>
+  <si>
+    <t>Sumaiya Binte  Islam</t>
+  </si>
+  <si>
+    <t>AL THIQA AL ALMYIAH PHARMACY - SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1215</t>
+  </si>
+  <si>
+    <t>10/01/2026</t>
+  </si>
+  <si>
+    <t>TA0180</t>
+  </si>
+  <si>
+    <t>SARA  KHALED ABDALGANI  ALJABER</t>
+  </si>
+  <si>
+    <t>SOFITEL PHARMACY - SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1474</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>TA0186</t>
+  </si>
+  <si>
+    <t>Shahbana Valiyakath Basheer Basheer</t>
+  </si>
+  <si>
+    <t>ALAIN PHARMACY- SOLE PROPRIETORSHIP L.L.C.- BRANCH  18</t>
+  </si>
+  <si>
+    <t>PF3270</t>
+  </si>
+  <si>
+    <t>Rabdan</t>
+  </si>
+  <si>
+    <t>TA0183</t>
+  </si>
+  <si>
+    <t>Farah  Nedal Mohammad Alnimrawi</t>
+  </si>
+  <si>
+    <t>ALAIN PHARMACY -  SOLE PROPRIETORSHIP L.L.C.-  BRANCH 7</t>
+  </si>
+  <si>
+    <t>PF3025</t>
+  </si>
+  <si>
+    <t>Asharij</t>
+  </si>
+  <si>
+    <t>GT28953</t>
+  </si>
+  <si>
+    <t>NAWAL ABDULLA KARAMA FARAJ Abdulla Karama ALKATHEERI</t>
+  </si>
+  <si>
+    <t>Forensics Allied Health</t>
+  </si>
+  <si>
+    <t>Pharmacokinetics</t>
+  </si>
+  <si>
+    <t>MEDICAL SERVICES ADMINISTRATION OF ABU DHABI POLICE GHQ</t>
+  </si>
+  <si>
+    <t>MF2125</t>
+  </si>
+  <si>
+    <t>08/06/2022</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>(forensic)</t>
+  </si>
+  <si>
+    <t>TA0765</t>
+  </si>
+  <si>
+    <t>AHMED ISAMELDIN  AHMED MOHAMED ABDU</t>
+  </si>
+  <si>
+    <t>AL THIQA AL THAKHASYSIYA PHARMACY- SOLE PROPRIETORSHIP L.L.C</t>
+  </si>
+  <si>
+    <t>PF1005</t>
+  </si>
+  <si>
+    <t>02/01/2026</t>
+  </si>
+  <si>
+    <t>TA0099</t>
+  </si>
+  <si>
+    <t>Roaa Zakrya Abo Safra</t>
+  </si>
+  <si>
+    <t>ALAIN CENTRAL PHARMACY - SOLE PROPRIETORSHIP L.L.C.</t>
+  </si>
+  <si>
+    <t>PF2550</t>
+  </si>
+  <si>
+    <t>Al Mas'oudi</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>TA0055</t>
+  </si>
+  <si>
+    <t>ZAINAB MUSHIR  IRAQI</t>
+  </si>
+  <si>
+    <t>01/03/2026</t>
+  </si>
+  <si>
+    <t>TA0056</t>
+  </si>
+  <si>
+    <t>EMAN  MOHAMMAD FATEHI SULEIMAN</t>
+  </si>
+  <si>
+    <t>TA0755</t>
+  </si>
+  <si>
+    <t>REEM ABDALLA  ALI ABDALLA</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>TA0763</t>
+  </si>
+  <si>
+    <t>Rahaf A.S.  Albhaisi</t>
+  </si>
+  <si>
+    <t>TA0800</t>
+  </si>
+  <si>
+    <t>RAMA IYAD ABED ALFATTAH HAMDAN</t>
+  </si>
+  <si>
+    <t>TA0552</t>
+  </si>
+  <si>
+    <t>DEEMA HASSAN MOUSSA HASSAN SALEM</t>
+  </si>
+  <si>
+    <t>PRESTIGE CARE PHARMACY</t>
+  </si>
+  <si>
+    <t>PF5519</t>
+  </si>
+  <si>
+    <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>TA0243</t>
+  </si>
+  <si>
+    <t>AYAH IBRAHIM  TAWFIK ISMAIL</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>TA0416</t>
+  </si>
+  <si>
+    <t>MARYAM SAMIR ABDELGAYED IBRAHIM ABDELHAMID ALLAM</t>
+  </si>
+  <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
+    <t>TA0002</t>
+  </si>
+  <si>
+    <t>AHMED HASSAN MOUSA HASSAN  SALEM</t>
+  </si>
+  <si>
+    <t>TA0225</t>
+  </si>
+  <si>
+    <t>Alaa Said Mahmoud Au Istaitieh</t>
+  </si>
+  <si>
+    <t>TA0470</t>
+  </si>
+  <si>
+    <t>ASHGAN IZZELDIEN MOHAMED  AHMED MALIK</t>
+  </si>
+  <si>
+    <t>AL TAHANI PHARMACY - SOLE PROPRIETORSHIP L.L.C.</t>
+  </si>
+  <si>
+    <t>PF1159</t>
+  </si>
+  <si>
+    <t>TA0608</t>
+  </si>
+  <si>
+    <t>Ahmad  Al Saleh</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>TA0643</t>
+  </si>
+  <si>
+    <t>Mohamed Magdi Fahim  Geneina</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>TA0231</t>
+  </si>
+  <si>
+    <t>NOUR MAGDI ABDELMOTLEB GOMAA</t>
+  </si>
+  <si>
+    <t>TA0244</t>
+  </si>
+  <si>
+    <t>SARA ABDELHADI MOHAMED ABDELHADI SALEM SHAMIYA</t>
+  </si>
+  <si>
+    <t>ROYAL TOP PHARMACY - SOLE PROPRIETORSHIP L.L.C.</t>
+  </si>
+  <si>
+    <t>PF5260</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>TA0292</t>
+  </si>
+  <si>
+    <t>MAEEN IZZ EDIN ALI BABIKIR</t>
+  </si>
+  <si>
+    <t>16/01/2025</t>
+  </si>
+  <si>
+    <t>TA0573</t>
+  </si>
+  <si>
+    <t>LUGAIN  AL SMADI</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
+    <t>TA0548</t>
+  </si>
+  <si>
+    <t>Safa  Koko</t>
+  </si>
+  <si>
+    <t>TA0577</t>
+  </si>
+  <si>
+    <t>RAYAN  ABDELMAGID ABDALLA  ABDELMAGID</t>
+  </si>
+  <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>TA0234</t>
+  </si>
+  <si>
+    <t>Naira Abdelrahman Adelrahman Mohamed Dawoud</t>
+  </si>
+  <si>
+    <t>TA0404</t>
+  </si>
+  <si>
+    <t>DANA HIKMAT   ABDUL KAREEM ODEH</t>
+  </si>
+  <si>
+    <t>N M C SPECIALTY HOSPITAL LTD</t>
+  </si>
+  <si>
+    <t>MF394</t>
+  </si>
+  <si>
+    <t>02/01/2025</t>
+  </si>
+  <si>
+    <t>TA0415</t>
+  </si>
+  <si>
+    <t>AMR MOHAMAD HAYAN RAHIMA</t>
+  </si>
+  <si>
+    <t>TA0039</t>
+  </si>
+  <si>
+    <t>MOHAMAD mohamed jihad ZEER</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
+    <t>TA0537</t>
+  </si>
+  <si>
+    <t>ALBATOOL ATWA HASAN ABUHUSSEIN</t>
+  </si>
+  <si>
+    <t>06/08/2025</t>
+  </si>
+  <si>
+    <t>TA0607</t>
+  </si>
+  <si>
+    <t>NUHA ASAAD AIRAN</t>
+  </si>
+  <si>
+    <t>PRESTIGE PHARMACY</t>
+  </si>
+  <si>
+    <t>PF2812</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>TA0678</t>
+  </si>
+  <si>
+    <t>JAMAL ALDORRA YAHYA JOBRAN  MOHAMED</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>GP16897</t>
+  </si>
+  <si>
+    <t>ASMA SAEED SALMEEN MOHAMMED SAEED SALMEEN MOHAMMED BINISHAQ</t>
+  </si>
+  <si>
+    <t>Resident</t>
+  </si>
+  <si>
+    <t>Pharmacist -Infectious diseases</t>
+  </si>
+  <si>
+    <t>CLEVELAND CLINIC ABUDHABI - SOLE PROPRIETORSHIP L.L.C. In-Patient Pharmacy</t>
+  </si>
+  <si>
+    <t>PF1750</t>
+  </si>
+  <si>
+    <t>24/10/2020</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>Allied Health Care Pharmacy Pharmacist</t>
+  </si>
+  <si>
+    <t>TA0228</t>
+  </si>
+  <si>
+    <t>Raneem Mahmoud AlJalam</t>
+  </si>
+  <si>
+    <t>TA0595</t>
+  </si>
+  <si>
+    <t>RAMA  SHAABOUK</t>
+  </si>
+  <si>
+    <t>05/10/2025</t>
+  </si>
+  <si>
+    <t>TA0222</t>
+  </si>
+  <si>
+    <t>Mohd Molham Mohd Bachir Sakkal</t>
+  </si>
+  <si>
+    <t>TA0567</t>
+  </si>
+  <si>
+    <t>ZEKRA HOSSAM ELSAYED ELERAKI ELDIASTI</t>
+  </si>
+  <si>
+    <t>24/08/2025</t>
+  </si>
+  <si>
+    <t>TA0561</t>
+  </si>
+  <si>
+    <t>LENA MOHAMMED   ALGHANEM</t>
+  </si>
+  <si>
+    <t>TA0580</t>
+  </si>
+  <si>
+    <t>HALA AHMAD  KASSAB</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>TA0077</t>
+  </si>
+  <si>
+    <t>Razan Kassem  Al Kais</t>
+  </si>
+  <si>
+    <t>TA0069</t>
+  </si>
+  <si>
+    <t>AYA REFAAT HASSAN ABDELKADER ELSHEHABI</t>
+  </si>
+  <si>
+    <t>22/08/2024</t>
+  </si>
+  <si>
+    <t>TA0074</t>
+  </si>
+  <si>
+    <t>Amal Gehad  Ahmed Kadas</t>
+  </si>
+  <si>
+    <t>TA0170</t>
+  </si>
+  <si>
+    <t>Mohamed  Hassan Mohamed  Hassan</t>
+  </si>
+  <si>
+    <t>ALAIN PHARMACY - SOLE PROPRIETORSHIP L.L.C.</t>
+  </si>
+  <si>
+    <t>PF1075</t>
+  </si>
+  <si>
+    <t>26/12/2024</t>
+  </si>
+  <si>
+    <t>TA0075</t>
+  </si>
+  <si>
+    <t>Sama Yasser Farouk Hassan El Noeimy</t>
+  </si>
+  <si>
+    <t>TA0209</t>
+  </si>
+  <si>
+    <t>Minu VINCENT VINCENT VELIYATHUKUDY Vincent</t>
+  </si>
+  <si>
+    <t>Reem Hospital L.L.C In-Patient Pharmacy</t>
+  </si>
+  <si>
+    <t>PF3122</t>
+  </si>
+  <si>
+    <t>15/11/2024</t>
+  </si>
+  <si>
+    <t>TA0094</t>
+  </si>
+  <si>
+    <t>FATEMEH MOUSA  ABDI</t>
+  </si>
+  <si>
+    <t>TA0073</t>
+  </si>
+  <si>
+    <t>FATIMA FAYEZ  AL SMADI</t>
   </si>
 </sst>
 </file>
@@ -1084,8 +1822,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1101,6 +1839,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D5AABF4D-3E74-45A6-B93B-323092700BA2}" name="Table2" displayName="Table2" ref="A1:P120" totalsRowShown="0">
+  <autoFilter ref="A1:P120" xr:uid="{D5AABF4D-3E74-45A6-B93B-323092700BA2}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{3BBF6ACD-8AC5-488C-8161-6735EED0823C}" name="Clinician License"/>
+    <tableColumn id="2" xr3:uid="{500A0891-B4F7-447C-A606-C3D9C319C333}" name="Clinician Name"/>
+    <tableColumn id="3" xr3:uid="{B0D23217-F0EA-4E5E-A3F1-AFB4BCF88807}" name="Major"/>
+    <tableColumn id="4" xr3:uid="{67BE21F4-8202-45B4-812A-F7BE8F88AC43}" name="Profession"/>
+    <tableColumn id="5" xr3:uid="{B206443C-3EBB-416F-8B74-57761FAB4F41}" name="Category"/>
+    <tableColumn id="6" xr3:uid="{C66F3AAD-8637-4E56-BBD5-3A6D8A0C4755}" name="Gender"/>
+    <tableColumn id="7" xr3:uid="{043C224D-8060-4C5F-85BC-A80A5FD66424}" name="Facility Name"/>
+    <tableColumn id="8" xr3:uid="{5145A2C0-9327-4BB4-B12D-68046AE69C12}" name="Facility License"/>
+    <tableColumn id="9" xr3:uid="{AEEA7398-BEEE-40C1-BF07-DE00F25F5F57}" name="Location"/>
+    <tableColumn id="10" xr3:uid="{75FCA1C1-8104-4E9C-A9F8-8418CE037749}" name="Facility Type"/>
+    <tableColumn id="11" xr3:uid="{4889F026-3F6B-438F-B67B-1A3B1B59BC4D}" name="Status"/>
+    <tableColumn id="12" xr3:uid="{3F1C9AAA-C099-4107-ABA1-20B79976F7E4}" name="From"/>
+    <tableColumn id="13" xr3:uid="{7792EEDA-AA87-48F6-97AF-0D0C645D5E99}" name="To"/>
+    <tableColumn id="14" xr3:uid="{A87F9D99-3A34-4998-B48F-19E0A26182CE}" name="Additional Titles"/>
+    <tableColumn id="15" xr3:uid="{C2ABE28B-C9ED-40D1-8FC1-32F9EBBD3218}" name="Remarks"/>
+    <tableColumn id="16" xr3:uid="{9329A0ED-C11B-4608-9A25-B74EF777B42C}" name="Privileges"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1420,67 +2183,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02908653-3E97-4C0A-9663-2681D23C4CED}">
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.7109375" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.42578125" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
     <col min="7" max="7" width="163.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
     <col min="9" max="9" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>213</v>
+      <c r="N1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -1490,9 +2260,6 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
       <c r="F2" t="s">
         <v>15</v>
       </c>
@@ -1508,14 +2275,9 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
       <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1524,9 +2286,6 @@
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
       <c r="F3" t="s">
         <v>15</v>
       </c>
@@ -1542,14 +2301,9 @@
       <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
       <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1558,9 +2312,6 @@
       <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
       <c r="F4" t="s">
         <v>15</v>
       </c>
@@ -1576,14 +2327,9 @@
       <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
       <c r="M4" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1592,9 +2338,6 @@
       <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
       <c r="F5" t="s">
         <v>15</v>
       </c>
@@ -1610,14 +2353,9 @@
       <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
       <c r="M5" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1626,9 +2364,6 @@
       <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
       <c r="F6" t="s">
         <v>15</v>
       </c>
@@ -1644,14 +2379,9 @@
       <c r="J6" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
       <c r="M6" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1660,9 +2390,6 @@
       <c r="B7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
       <c r="F7" t="s">
         <v>15</v>
       </c>
@@ -1678,14 +2405,9 @@
       <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
       <c r="M7" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1694,9 +2416,6 @@
       <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
       <c r="F8" t="s">
         <v>15</v>
       </c>
@@ -1712,14 +2431,9 @@
       <c r="J8" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
       <c r="M8" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1728,9 +2442,6 @@
       <c r="B9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
       <c r="F9" t="s">
         <v>15</v>
       </c>
@@ -1746,14 +2457,9 @@
       <c r="J9" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
       <c r="M9" t="s">
         <v>20</v>
       </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1762,9 +2468,6 @@
       <c r="B10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
       <c r="F10" t="s">
         <v>15</v>
       </c>
@@ -1780,14 +2483,9 @@
       <c r="J10" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
       <c r="M10" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1796,9 +2494,6 @@
       <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
       <c r="F11" t="s">
         <v>15</v>
       </c>
@@ -1814,14 +2509,9 @@
       <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
       <c r="M11" t="s">
         <v>43</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1848,7 +2538,6 @@
       <c r="H12" t="s">
         <v>71</v>
       </c>
-      <c r="I12" s="2"/>
       <c r="J12" t="s">
         <v>72</v>
       </c>
@@ -1861,9 +2550,6 @@
       <c r="M12" t="s">
         <v>75</v>
       </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1905,9 +2591,6 @@
       <c r="M13" t="s">
         <v>86</v>
       </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1916,9 +2599,6 @@
       <c r="B14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
       <c r="F14" t="s">
         <v>15</v>
       </c>
@@ -1943,9 +2623,6 @@
       <c r="M14" t="s">
         <v>86</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1987,9 +2664,6 @@
       <c r="M15" t="s">
         <v>86</v>
       </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -2031,82 +2705,78 @@
       <c r="M16" t="s">
         <v>86</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="K17" t="s">
         <v>73</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s">
         <v>73</v>
@@ -2117,40 +2787,37 @@
       <c r="M18" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K19" t="s">
         <v>73</v>
@@ -2161,40 +2828,37 @@
       <c r="M19" t="s">
         <v>75</v>
       </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I20" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="K20" t="s">
         <v>73</v>
@@ -2205,60 +2869,54 @@
       <c r="M20" t="s">
         <v>75</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
         <v>73</v>
       </c>
       <c r="L21" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="M21" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
         <v>78</v>
@@ -2270,148 +2928,136 @@
         <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I22" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K22" t="s">
         <v>73</v>
       </c>
       <c r="L22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M22" t="s">
-        <v>143</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I23" t="s">
         <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="K23" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="L23" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="M23" t="s">
-        <v>149</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I24" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="J24" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K24" t="s">
         <v>73</v>
       </c>
       <c r="L24" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s">
-        <v>149</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H25" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
       <c r="J25" t="s">
         <v>72</v>
@@ -2420,84 +3066,80 @@
         <v>73</v>
       </c>
       <c r="L25" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="M25" t="s">
-        <v>161</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H26" t="s">
-        <v>165</v>
-      </c>
-      <c r="I26" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="I26" t="s">
+        <v>170</v>
+      </c>
       <c r="J26" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="K26" t="s">
         <v>73</v>
       </c>
       <c r="L26" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="M26" t="s">
-        <v>149</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="I27" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -2506,41 +3148,40 @@
         <v>73</v>
       </c>
       <c r="L27" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s">
-        <v>149</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
-      </c>
-      <c r="I28" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="I28" t="s">
+        <v>180</v>
+      </c>
       <c r="J28" t="s">
         <v>72</v>
       </c>
@@ -2548,60 +3189,54 @@
         <v>73</v>
       </c>
       <c r="L28" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="M28" t="s">
-        <v>149</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
         <v>99</v>
       </c>
       <c r="G29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J29" t="s">
-        <v>183</v>
+        <v>37</v>
       </c>
       <c r="K29" t="s">
         <v>73</v>
       </c>
       <c r="L29" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="M29" t="s">
-        <v>185</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>186</v>
       </c>
@@ -2609,25 +3244,25 @@
         <v>187</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="I30" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="J30" t="s">
         <v>19</v>
@@ -2636,42 +3271,30 @@
         <v>73</v>
       </c>
       <c r="L30" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s">
-        <v>185</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="F31" t="s">
         <v>99</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I31" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
         <v>72</v>
@@ -2680,124 +3303,121 @@
         <v>73</v>
       </c>
       <c r="L31" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="M31" t="s">
-        <v>185</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>195</v>
+        <v>57</v>
       </c>
       <c r="H32" t="s">
-        <v>196</v>
+        <v>58</v>
       </c>
       <c r="I32" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="J32" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s">
         <v>73</v>
       </c>
       <c r="L32" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="M32" t="s">
-        <v>185</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="E33" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G33" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H33" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K33" t="s">
         <v>73</v>
       </c>
       <c r="L33" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="M33" t="s">
-        <v>185</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" t="s">
+        <v>150</v>
+      </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H34" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="J34" t="s">
         <v>72</v>
@@ -2806,42 +3426,39 @@
         <v>73</v>
       </c>
       <c r="L34" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="M34" t="s">
-        <v>208</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G35" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="I35" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -2850,42 +3467,39 @@
         <v>73</v>
       </c>
       <c r="L35" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="M35" t="s">
-        <v>185</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>221</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H36" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="I36" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
         <v>72</v>
@@ -2894,86 +3508,80 @@
         <v>73</v>
       </c>
       <c r="L36" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="M36" t="s">
-        <v>185</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H37" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I37" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
         <v>73</v>
       </c>
       <c r="L37" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M37" t="s">
-        <v>224</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D38" t="s">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F38" t="s">
         <v>99</v>
       </c>
       <c r="G38" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H38" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I38" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="J38" t="s">
         <v>19</v>
@@ -2982,197 +3590,182 @@
         <v>73</v>
       </c>
       <c r="L38" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s">
-        <v>224</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H39" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="J39" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
         <v>73</v>
       </c>
       <c r="L39" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M39" t="s">
-        <v>161</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K40" t="s">
         <v>73</v>
       </c>
       <c r="L40" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="M40" t="s">
-        <v>245</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="2"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C41" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>117</v>
+        <v>249</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H41" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="K41" t="s">
         <v>73</v>
       </c>
       <c r="L41" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M41" t="s">
-        <v>245</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E42" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H42" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I42" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="K42" t="s">
         <v>73</v>
       </c>
       <c r="L42" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M42" t="s">
-        <v>245</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C43" t="s">
         <v>78</v>
@@ -3187,148 +3780,139 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I43" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="J43" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
         <v>73</v>
       </c>
       <c r="L43" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="M43" t="s">
-        <v>245</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E44" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F44" t="s">
         <v>99</v>
       </c>
       <c r="G44" t="s">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>264</v>
+        <v>101</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="J44" t="s">
-        <v>265</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s">
         <v>73</v>
       </c>
       <c r="L44" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M44" t="s">
-        <v>267</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G45" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H45" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I45" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J45" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
         <v>73</v>
       </c>
       <c r="L45" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M45" t="s">
-        <v>267</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>281</v>
       </c>
       <c r="I46" t="s">
-        <v>59</v>
+        <v>282</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K46" t="s">
         <v>73</v>
@@ -3339,40 +3923,37 @@
       <c r="M46" t="s">
         <v>277</v>
       </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="E47" t="s">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="F47" t="s">
         <v>99</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="H47" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="I47" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K47" t="s">
         <v>73</v>
@@ -3383,37 +3964,34 @@
       <c r="M47" t="s">
         <v>277</v>
       </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="E48" t="s">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="F48" t="s">
         <v>99</v>
       </c>
       <c r="G48" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="H48" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="I48" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -3422,58 +4000,49 @@
         <v>73</v>
       </c>
       <c r="L48" t="s">
+        <v>287</v>
+      </c>
+      <c r="M48" t="s">
         <v>288</v>
       </c>
-      <c r="M48" t="s">
-        <v>289</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>289</v>
+      </c>
+      <c r="B49" t="s">
         <v>290</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" t="s">
         <v>291</v>
       </c>
-      <c r="C49" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>292</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H49" t="s">
-        <v>293</v>
-      </c>
-      <c r="I49" t="s">
         <v>294</v>
       </c>
       <c r="J49" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K49" t="s">
         <v>73</v>
       </c>
       <c r="L49" t="s">
+        <v>287</v>
+      </c>
+      <c r="M49" t="s">
         <v>288</v>
       </c>
-      <c r="M49" t="s">
-        <v>289</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -3483,25 +4052,25 @@
         <v>296</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>195</v>
+        <v>297</v>
       </c>
       <c r="H50" t="s">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="I50" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
         <v>37</v>
@@ -3510,42 +4079,39 @@
         <v>73</v>
       </c>
       <c r="L50" t="s">
+        <v>287</v>
+      </c>
+      <c r="M50" t="s">
         <v>288</v>
       </c>
-      <c r="M50" t="s">
-        <v>289</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B51" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>285</v>
+        <v>57</v>
       </c>
       <c r="H51" t="s">
-        <v>286</v>
+        <v>58</v>
       </c>
       <c r="I51" t="s">
-        <v>287</v>
+        <v>59</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -3554,33 +4120,30 @@
         <v>73</v>
       </c>
       <c r="L51" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M51" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
+        <v>302</v>
+      </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B52" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>303</v>
+        <v>241</v>
       </c>
       <c r="E52" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
         <v>305</v>
@@ -3588,22 +4151,21 @@
       <c r="H52" t="s">
         <v>306</v>
       </c>
-      <c r="I52" s="2"/>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
       <c r="J52" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="K52" t="s">
         <v>73</v>
       </c>
       <c r="L52" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M52" t="s">
-        <v>300</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
+        <v>302</v>
+      </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3613,13 +4175,13 @@
         <v>308</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
@@ -3631,7 +4193,7 @@
         <v>310</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J53" t="s">
         <v>37</v>
@@ -3640,14 +4202,11 @@
         <v>73</v>
       </c>
       <c r="L53" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M53" t="s">
-        <v>300</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
+        <v>302</v>
+      </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -3660,22 +4219,22 @@
         <v>67</v>
       </c>
       <c r="D54" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E54" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F54" t="s">
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="I54" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="J54" t="s">
         <v>19</v>
@@ -3689,9 +4248,6 @@
       <c r="M54" t="s">
         <v>314</v>
       </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -3701,16 +4257,16 @@
         <v>316</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G55" t="s">
         <v>317</v>
@@ -3722,7 +4278,7 @@
         <v>25</v>
       </c>
       <c r="J55" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="K55" t="s">
         <v>73</v>
@@ -3733,9 +4289,6 @@
       <c r="M55" t="s">
         <v>314</v>
       </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -3754,16 +4307,16 @@
         <v>80</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G56" t="s">
-        <v>321</v>
+        <v>183</v>
       </c>
       <c r="H56" t="s">
-        <v>322</v>
+        <v>184</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="J56" t="s">
         <v>37</v>
@@ -3772,16 +4325,13 @@
         <v>73</v>
       </c>
       <c r="L56" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="M56" t="s">
-        <v>314</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>323</v>
       </c>
@@ -3789,28 +4339,28 @@
         <v>324</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>178</v>
+        <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="F57" t="s">
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>229</v>
+        <v>41</v>
       </c>
       <c r="H57" t="s">
-        <v>230</v>
+        <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="J57" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K57" t="s">
         <v>73</v>
@@ -3821,99 +4371,2391 @@
       <c r="M57" t="s">
         <v>326</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N57"/>
+      <c r="O57" t="s">
+        <v>327</v>
+      </c>
+      <c r="P57" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F58" t="s">
         <v>99</v>
       </c>
       <c r="G58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H58" t="s">
-        <v>330</v>
-      </c>
-      <c r="I58" t="s">
-        <v>25</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="I58"/>
       <c r="J58" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K58" t="s">
         <v>73</v>
       </c>
       <c r="L58" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M58" t="s">
-        <v>326</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B59" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F59" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>195</v>
+        <v>336</v>
       </c>
       <c r="H59" t="s">
-        <v>196</v>
+        <v>337</v>
       </c>
       <c r="I59" t="s">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="J59" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="K59" t="s">
         <v>73</v>
       </c>
       <c r="L59" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M59" t="s">
-        <v>334</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N59"/>
+      <c r="O59" t="s">
+        <v>327</v>
+      </c>
+      <c r="P59" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>340</v>
+      </c>
+      <c r="B60" t="s">
+        <v>341</v>
+      </c>
+      <c r="C60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" t="s">
+        <v>103</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>342</v>
+      </c>
+      <c r="H60" t="s">
+        <v>343</v>
+      </c>
+      <c r="I60" t="s">
+        <v>344</v>
+      </c>
+      <c r="J60" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" t="s">
+        <v>73</v>
+      </c>
+      <c r="L60" t="s">
+        <v>345</v>
+      </c>
+      <c r="M60" t="s">
+        <v>346</v>
+      </c>
+      <c r="N60"/>
+      <c r="O60" t="s">
+        <v>327</v>
+      </c>
+      <c r="P60" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>347</v>
+      </c>
+      <c r="B61" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" t="s">
+        <v>103</v>
+      </c>
+      <c r="F61" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" t="s">
+        <v>349</v>
+      </c>
+      <c r="H61" t="s">
+        <v>350</v>
+      </c>
+      <c r="I61" t="s">
+        <v>117</v>
+      </c>
+      <c r="J61" t="s">
+        <v>26</v>
+      </c>
+      <c r="K61" t="s">
+        <v>73</v>
+      </c>
+      <c r="L61" t="s">
+        <v>351</v>
+      </c>
+      <c r="M61" t="s">
+        <v>352</v>
+      </c>
+      <c r="N61"/>
+      <c r="O61" t="s">
+        <v>327</v>
+      </c>
+      <c r="P61" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>353</v>
+      </c>
+      <c r="B62" t="s">
+        <v>354</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s">
+        <v>355</v>
+      </c>
+      <c r="F62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" t="s">
+        <v>356</v>
+      </c>
+      <c r="H62" t="s">
+        <v>357</v>
+      </c>
+      <c r="I62" t="s">
+        <v>244</v>
+      </c>
+      <c r="J62" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" t="s">
+        <v>73</v>
+      </c>
+      <c r="L62" t="s">
+        <v>358</v>
+      </c>
+      <c r="M62" t="s">
+        <v>359</v>
+      </c>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B63" t="s">
+        <v>361</v>
+      </c>
+      <c r="C63" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="s">
+        <v>103</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>362</v>
+      </c>
+      <c r="H63" t="s">
+        <v>363</v>
+      </c>
+      <c r="I63" t="s">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63" t="s">
+        <v>73</v>
+      </c>
+      <c r="L63" t="s">
+        <v>364</v>
+      </c>
+      <c r="M63" t="s">
+        <v>365</v>
+      </c>
+      <c r="N63"/>
+      <c r="O63" t="s">
+        <v>327</v>
+      </c>
+      <c r="P63" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>366</v>
+      </c>
+      <c r="B64" t="s">
+        <v>367</v>
+      </c>
+      <c r="C64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
+        <v>355</v>
+      </c>
+      <c r="F64" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" t="s">
+        <v>368</v>
+      </c>
+      <c r="H64" t="s">
+        <v>369</v>
+      </c>
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" t="s">
+        <v>26</v>
+      </c>
+      <c r="K64" t="s">
+        <v>73</v>
+      </c>
+      <c r="L64" t="s">
+        <v>370</v>
+      </c>
+      <c r="M64" t="s">
+        <v>339</v>
+      </c>
+      <c r="N64"/>
+      <c r="O64" t="s">
+        <v>327</v>
+      </c>
+      <c r="P64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>371</v>
+      </c>
+      <c r="B65" t="s">
+        <v>372</v>
+      </c>
+      <c r="C65" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
+        <v>355</v>
+      </c>
+      <c r="F65" t="s">
+        <v>99</v>
+      </c>
+      <c r="G65" t="s">
+        <v>62</v>
+      </c>
+      <c r="H65" t="s">
+        <v>63</v>
+      </c>
+      <c r="I65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J65" t="s">
+        <v>26</v>
+      </c>
+      <c r="K65" t="s">
+        <v>73</v>
+      </c>
+      <c r="L65" t="s">
+        <v>373</v>
+      </c>
+      <c r="M65" t="s">
+        <v>374</v>
+      </c>
+      <c r="N65"/>
+      <c r="O65" t="s">
+        <v>327</v>
+      </c>
+      <c r="P65" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>375</v>
+      </c>
+      <c r="B66" t="s">
+        <v>376</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" t="s">
+        <v>355</v>
+      </c>
+      <c r="F66" t="s">
+        <v>99</v>
+      </c>
+      <c r="G66" t="s">
+        <v>377</v>
+      </c>
+      <c r="H66" t="s">
+        <v>378</v>
+      </c>
+      <c r="I66" t="s">
+        <v>282</v>
+      </c>
+      <c r="J66" t="s">
+        <v>26</v>
+      </c>
+      <c r="K66" t="s">
+        <v>73</v>
+      </c>
+      <c r="L66" t="s">
+        <v>379</v>
+      </c>
+      <c r="M66" t="s">
+        <v>380</v>
+      </c>
+      <c r="N66"/>
+      <c r="O66" t="s">
+        <v>327</v>
+      </c>
+      <c r="P66" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>381</v>
+      </c>
+      <c r="B67" t="s">
+        <v>382</v>
+      </c>
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>355</v>
+      </c>
+      <c r="F67" t="s">
+        <v>99</v>
+      </c>
+      <c r="G67" t="s">
+        <v>383</v>
+      </c>
+      <c r="H67" t="s">
+        <v>384</v>
+      </c>
+      <c r="I67" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L67" t="s">
+        <v>385</v>
+      </c>
+      <c r="M67" t="s">
+        <v>255</v>
+      </c>
+      <c r="N67"/>
+      <c r="O67" t="s">
+        <v>327</v>
+      </c>
+      <c r="P67" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>386</v>
+      </c>
+      <c r="B68" t="s">
+        <v>387</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>355</v>
+      </c>
+      <c r="F68" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" t="s">
+        <v>388</v>
+      </c>
+      <c r="H68" t="s">
+        <v>389</v>
+      </c>
+      <c r="I68" t="s">
+        <v>275</v>
+      </c>
+      <c r="J68" t="s">
+        <v>26</v>
+      </c>
+      <c r="K68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L68" t="s">
+        <v>390</v>
+      </c>
+      <c r="M68" t="s">
+        <v>391</v>
+      </c>
+      <c r="N68"/>
+      <c r="O68" t="s">
+        <v>327</v>
+      </c>
+      <c r="P68" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>392</v>
+      </c>
+      <c r="B69" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>355</v>
+      </c>
+      <c r="F69" t="s">
+        <v>99</v>
+      </c>
+      <c r="G69" t="s">
+        <v>394</v>
+      </c>
+      <c r="H69" t="s">
+        <v>395</v>
+      </c>
+      <c r="I69" t="s">
+        <v>396</v>
+      </c>
+      <c r="J69" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" t="s">
+        <v>73</v>
+      </c>
+      <c r="L69" t="s">
+        <v>397</v>
+      </c>
+      <c r="M69" t="s">
+        <v>398</v>
+      </c>
+      <c r="N69"/>
+      <c r="O69" t="s">
+        <v>327</v>
+      </c>
+      <c r="P69" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" t="s">
+        <v>407</v>
+      </c>
+      <c r="C70" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70" t="s">
+        <v>401</v>
+      </c>
+      <c r="E70" t="s">
+        <v>402</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
+        <v>408</v>
+      </c>
+      <c r="H70" t="s">
+        <v>409</v>
+      </c>
+      <c r="I70" t="s">
+        <v>410</v>
+      </c>
+      <c r="J70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>411</v>
+      </c>
+      <c r="B71" t="s">
+        <v>412</v>
+      </c>
+      <c r="C71" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" t="s">
+        <v>401</v>
+      </c>
+      <c r="E71" t="s">
+        <v>402</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
+        <v>413</v>
+      </c>
+      <c r="H71" t="s">
+        <v>414</v>
+      </c>
+      <c r="I71" t="s">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>416</v>
+      </c>
+      <c r="B72" t="s">
+        <v>417</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>401</v>
+      </c>
+      <c r="E72" t="s">
+        <v>402</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
+        <v>418</v>
+      </c>
+      <c r="H72" t="s">
+        <v>419</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>421</v>
+      </c>
+      <c r="B73" t="s">
+        <v>422</v>
+      </c>
+      <c r="C73" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" t="s">
+        <v>401</v>
+      </c>
+      <c r="E73" t="s">
+        <v>402</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
+        <v>423</v>
+      </c>
+      <c r="H73" t="s">
+        <v>424</v>
+      </c>
+      <c r="I73" t="s">
+        <v>410</v>
+      </c>
+      <c r="J73" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>426</v>
+      </c>
+      <c r="B74" t="s">
+        <v>427</v>
+      </c>
+      <c r="C74" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" t="s">
+        <v>401</v>
+      </c>
+      <c r="E74" t="s">
+        <v>402</v>
+      </c>
+      <c r="F74" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s">
+        <v>428</v>
+      </c>
+      <c r="H74" t="s">
+        <v>429</v>
+      </c>
+      <c r="I74" t="s">
+        <v>430</v>
+      </c>
+      <c r="J74" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>431</v>
+      </c>
+      <c r="B75" t="s">
+        <v>432</v>
+      </c>
+      <c r="C75" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" t="s">
+        <v>401</v>
+      </c>
+      <c r="E75" t="s">
+        <v>402</v>
+      </c>
+      <c r="F75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s">
+        <v>433</v>
+      </c>
+      <c r="H75" t="s">
+        <v>434</v>
+      </c>
+      <c r="I75" t="s">
+        <v>435</v>
+      </c>
+      <c r="J75" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>436</v>
+      </c>
+      <c r="B76" t="s">
+        <v>437</v>
+      </c>
+      <c r="C76" t="s">
+        <v>120</v>
+      </c>
+      <c r="D76" t="s">
+        <v>438</v>
+      </c>
+      <c r="E76" t="s">
+        <v>439</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>440</v>
+      </c>
+      <c r="H76" t="s">
+        <v>441</v>
+      </c>
+      <c r="I76" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" t="s">
+        <v>72</v>
+      </c>
+      <c r="K76" t="s">
+        <v>73</v>
+      </c>
+      <c r="L76" t="s">
+        <v>442</v>
+      </c>
+      <c r="M76" t="s">
+        <v>443</v>
+      </c>
+      <c r="O76" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>445</v>
+      </c>
+      <c r="B77" t="s">
+        <v>446</v>
+      </c>
+      <c r="C77" t="s">
+        <v>120</v>
+      </c>
+      <c r="D77" t="s">
+        <v>401</v>
+      </c>
+      <c r="E77" t="s">
+        <v>402</v>
+      </c>
+      <c r="F77" t="s">
+        <v>99</v>
+      </c>
+      <c r="G77" t="s">
+        <v>447</v>
+      </c>
+      <c r="H77" t="s">
+        <v>448</v>
+      </c>
+      <c r="I77" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>450</v>
+      </c>
+      <c r="B78" t="s">
+        <v>451</v>
+      </c>
+      <c r="C78" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" t="s">
+        <v>401</v>
+      </c>
+      <c r="E78" t="s">
+        <v>402</v>
+      </c>
+      <c r="F78" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s">
+        <v>452</v>
+      </c>
+      <c r="H78" t="s">
+        <v>453</v>
+      </c>
+      <c r="I78" t="s">
+        <v>454</v>
+      </c>
+      <c r="J78" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>456</v>
+      </c>
+      <c r="B79" t="s">
+        <v>457</v>
+      </c>
+      <c r="C79" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" t="s">
+        <v>401</v>
+      </c>
+      <c r="E79" t="s">
+        <v>402</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>403</v>
+      </c>
+      <c r="H79" t="s">
+        <v>404</v>
+      </c>
+      <c r="I79" t="s">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>459</v>
+      </c>
+      <c r="B80" t="s">
+        <v>460</v>
+      </c>
+      <c r="C80" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" t="s">
+        <v>401</v>
+      </c>
+      <c r="E80" t="s">
+        <v>402</v>
+      </c>
+      <c r="F80" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" t="s">
+        <v>403</v>
+      </c>
+      <c r="H80" t="s">
+        <v>404</v>
+      </c>
+      <c r="I80" t="s">
+        <v>83</v>
+      </c>
+      <c r="J80" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" t="s">
+        <v>462</v>
+      </c>
+      <c r="C81" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" t="s">
+        <v>401</v>
+      </c>
+      <c r="E81" t="s">
+        <v>402</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s">
+        <v>403</v>
+      </c>
+      <c r="H81" t="s">
+        <v>404</v>
+      </c>
+      <c r="I81" t="s">
+        <v>83</v>
+      </c>
+      <c r="J81" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>464</v>
+      </c>
+      <c r="B82" t="s">
+        <v>465</v>
+      </c>
+      <c r="C82" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" t="s">
+        <v>401</v>
+      </c>
+      <c r="E82" t="s">
+        <v>402</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>403</v>
+      </c>
+      <c r="H82" t="s">
+        <v>404</v>
+      </c>
+      <c r="I82" t="s">
+        <v>83</v>
+      </c>
+      <c r="J82" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>466</v>
+      </c>
+      <c r="B83" t="s">
+        <v>467</v>
+      </c>
+      <c r="C83" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" t="s">
+        <v>401</v>
+      </c>
+      <c r="E83" t="s">
+        <v>402</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>447</v>
+      </c>
+      <c r="H83" t="s">
+        <v>448</v>
+      </c>
+      <c r="I83" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>468</v>
+      </c>
+      <c r="B84" t="s">
+        <v>469</v>
+      </c>
+      <c r="C84" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" t="s">
+        <v>401</v>
+      </c>
+      <c r="E84" t="s">
+        <v>402</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s">
+        <v>470</v>
+      </c>
+      <c r="H84" t="s">
+        <v>471</v>
+      </c>
+      <c r="J84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>473</v>
+      </c>
+      <c r="B85" t="s">
+        <v>474</v>
+      </c>
+      <c r="C85" t="s">
+        <v>120</v>
+      </c>
+      <c r="D85" t="s">
+        <v>401</v>
+      </c>
+      <c r="E85" t="s">
+        <v>402</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>447</v>
+      </c>
+      <c r="H85" t="s">
+        <v>448</v>
+      </c>
+      <c r="I85" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>476</v>
+      </c>
+      <c r="B86" t="s">
+        <v>477</v>
+      </c>
+      <c r="C86" t="s">
+        <v>120</v>
+      </c>
+      <c r="D86" t="s">
+        <v>401</v>
+      </c>
+      <c r="E86" t="s">
+        <v>402</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s">
+        <v>447</v>
+      </c>
+      <c r="H86" t="s">
+        <v>448</v>
+      </c>
+      <c r="I86" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>479</v>
+      </c>
+      <c r="B87" t="s">
+        <v>480</v>
+      </c>
+      <c r="C87" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" t="s">
+        <v>401</v>
+      </c>
+      <c r="E87" t="s">
+        <v>402</v>
+      </c>
+      <c r="F87" t="s">
+        <v>99</v>
+      </c>
+      <c r="G87" t="s">
+        <v>403</v>
+      </c>
+      <c r="H87" t="s">
+        <v>404</v>
+      </c>
+      <c r="I87" t="s">
+        <v>83</v>
+      </c>
+      <c r="J87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>481</v>
+      </c>
+      <c r="B88" t="s">
+        <v>482</v>
+      </c>
+      <c r="C88" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" t="s">
+        <v>401</v>
+      </c>
+      <c r="E88" t="s">
+        <v>402</v>
+      </c>
+      <c r="F88" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s">
+        <v>413</v>
+      </c>
+      <c r="H88" t="s">
+        <v>414</v>
+      </c>
+      <c r="I88" t="s">
+        <v>83</v>
+      </c>
+      <c r="J88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>483</v>
+      </c>
+      <c r="B89" t="s">
+        <v>484</v>
+      </c>
+      <c r="C89" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" t="s">
+        <v>401</v>
+      </c>
+      <c r="E89" t="s">
+        <v>402</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
+        <v>485</v>
+      </c>
+      <c r="H89" t="s">
+        <v>486</v>
+      </c>
+      <c r="I89" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>487</v>
+      </c>
+      <c r="B90" t="s">
+        <v>488</v>
+      </c>
+      <c r="C90" t="s">
+        <v>120</v>
+      </c>
+      <c r="D90" t="s">
+        <v>401</v>
+      </c>
+      <c r="E90" t="s">
+        <v>402</v>
+      </c>
+      <c r="F90" t="s">
+        <v>99</v>
+      </c>
+      <c r="G90" t="s">
+        <v>447</v>
+      </c>
+      <c r="H90" t="s">
+        <v>448</v>
+      </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>490</v>
+      </c>
+      <c r="B91" t="s">
+        <v>491</v>
+      </c>
+      <c r="C91" t="s">
+        <v>120</v>
+      </c>
+      <c r="D91" t="s">
+        <v>401</v>
+      </c>
+      <c r="E91" t="s">
+        <v>402</v>
+      </c>
+      <c r="F91" t="s">
+        <v>99</v>
+      </c>
+      <c r="G91" t="s">
+        <v>403</v>
+      </c>
+      <c r="H91" t="s">
+        <v>404</v>
+      </c>
+      <c r="I91" t="s">
+        <v>83</v>
+      </c>
+      <c r="J91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>493</v>
+      </c>
+      <c r="B92" t="s">
+        <v>494</v>
+      </c>
+      <c r="C92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D92" t="s">
+        <v>401</v>
+      </c>
+      <c r="E92" t="s">
+        <v>402</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s">
+        <v>447</v>
+      </c>
+      <c r="H92" t="s">
+        <v>448</v>
+      </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>495</v>
+      </c>
+      <c r="B93" t="s">
+        <v>496</v>
+      </c>
+      <c r="C93" t="s">
+        <v>120</v>
+      </c>
+      <c r="D93" t="s">
+        <v>401</v>
+      </c>
+      <c r="E93" t="s">
+        <v>402</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
+        <v>497</v>
+      </c>
+      <c r="H93" t="s">
+        <v>498</v>
+      </c>
+      <c r="I93" t="s">
+        <v>125</v>
+      </c>
+      <c r="J93" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>500</v>
+      </c>
+      <c r="B94" t="s">
+        <v>501</v>
+      </c>
+      <c r="C94" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" t="s">
+        <v>401</v>
+      </c>
+      <c r="E94" t="s">
+        <v>402</v>
+      </c>
+      <c r="F94" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s">
+        <v>413</v>
+      </c>
+      <c r="H94" t="s">
+        <v>414</v>
+      </c>
+      <c r="I94" t="s">
+        <v>83</v>
+      </c>
+      <c r="J94" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>503</v>
+      </c>
+      <c r="B95" t="s">
+        <v>504</v>
+      </c>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" t="s">
+        <v>401</v>
+      </c>
+      <c r="E95" t="s">
+        <v>402</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s">
+        <v>403</v>
+      </c>
+      <c r="H95" t="s">
+        <v>404</v>
+      </c>
+      <c r="I95" t="s">
+        <v>83</v>
+      </c>
+      <c r="J95" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>506</v>
+      </c>
+      <c r="B96" t="s">
+        <v>507</v>
+      </c>
+      <c r="C96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D96" t="s">
+        <v>401</v>
+      </c>
+      <c r="E96" t="s">
+        <v>402</v>
+      </c>
+      <c r="F96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s">
+        <v>418</v>
+      </c>
+      <c r="H96" t="s">
+        <v>419</v>
+      </c>
+      <c r="I96" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>508</v>
+      </c>
+      <c r="B97" t="s">
+        <v>509</v>
+      </c>
+      <c r="C97" t="s">
+        <v>120</v>
+      </c>
+      <c r="D97" t="s">
+        <v>401</v>
+      </c>
+      <c r="E97" t="s">
+        <v>402</v>
+      </c>
+      <c r="F97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s">
+        <v>413</v>
+      </c>
+      <c r="H97" t="s">
+        <v>414</v>
+      </c>
+      <c r="I97" t="s">
+        <v>83</v>
+      </c>
+      <c r="J97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>511</v>
+      </c>
+      <c r="B98" t="s">
+        <v>512</v>
+      </c>
+      <c r="C98" t="s">
+        <v>120</v>
+      </c>
+      <c r="D98" t="s">
+        <v>401</v>
+      </c>
+      <c r="E98" t="s">
+        <v>402</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s">
+        <v>403</v>
+      </c>
+      <c r="H98" t="s">
+        <v>404</v>
+      </c>
+      <c r="I98" t="s">
+        <v>83</v>
+      </c>
+      <c r="J98" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>513</v>
+      </c>
+      <c r="B99" t="s">
+        <v>514</v>
+      </c>
+      <c r="C99" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" t="s">
+        <v>401</v>
+      </c>
+      <c r="E99" t="s">
+        <v>402</v>
+      </c>
+      <c r="F99" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" t="s">
+        <v>515</v>
+      </c>
+      <c r="H99" t="s">
+        <v>516</v>
+      </c>
+      <c r="I99" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" t="s">
+        <v>19</v>
+      </c>
+      <c r="M99" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>518</v>
+      </c>
+      <c r="B100" t="s">
+        <v>519</v>
+      </c>
+      <c r="C100" t="s">
+        <v>120</v>
+      </c>
+      <c r="D100" t="s">
+        <v>401</v>
+      </c>
+      <c r="E100" t="s">
+        <v>402</v>
+      </c>
+      <c r="F100" t="s">
+        <v>99</v>
+      </c>
+      <c r="G100" t="s">
+        <v>403</v>
+      </c>
+      <c r="H100" t="s">
+        <v>404</v>
+      </c>
+      <c r="I100" t="s">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>520</v>
+      </c>
+      <c r="B101" t="s">
+        <v>521</v>
+      </c>
+      <c r="C101" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" t="s">
+        <v>401</v>
+      </c>
+      <c r="E101" t="s">
+        <v>402</v>
+      </c>
+      <c r="F101" t="s">
+        <v>99</v>
+      </c>
+      <c r="G101" t="s">
+        <v>447</v>
+      </c>
+      <c r="H101" t="s">
+        <v>448</v>
+      </c>
+      <c r="I101" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>523</v>
+      </c>
+      <c r="B102" t="s">
+        <v>524</v>
+      </c>
+      <c r="C102" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" t="s">
+        <v>401</v>
+      </c>
+      <c r="E102" t="s">
+        <v>402</v>
+      </c>
+      <c r="F102" t="s">
+        <v>99</v>
+      </c>
+      <c r="G102" t="s">
+        <v>470</v>
+      </c>
+      <c r="H102" t="s">
+        <v>471</v>
+      </c>
+      <c r="J102" t="s">
+        <v>26</v>
+      </c>
+      <c r="M102" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>526</v>
+      </c>
+      <c r="B103" t="s">
+        <v>527</v>
+      </c>
+      <c r="C103" t="s">
+        <v>120</v>
+      </c>
+      <c r="D103" t="s">
+        <v>401</v>
+      </c>
+      <c r="E103" t="s">
+        <v>402</v>
+      </c>
+      <c r="F103" t="s">
+        <v>15</v>
+      </c>
+      <c r="G103" t="s">
+        <v>528</v>
+      </c>
+      <c r="H103" t="s">
+        <v>529</v>
+      </c>
+      <c r="I103" t="s">
+        <v>25</v>
+      </c>
+      <c r="J103" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>531</v>
+      </c>
+      <c r="B104" t="s">
+        <v>532</v>
+      </c>
+      <c r="C104" t="s">
+        <v>120</v>
+      </c>
+      <c r="D104" t="s">
+        <v>401</v>
+      </c>
+      <c r="E104" t="s">
+        <v>402</v>
+      </c>
+      <c r="F104" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s">
+        <v>418</v>
+      </c>
+      <c r="H104" t="s">
+        <v>419</v>
+      </c>
+      <c r="I104" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>534</v>
+      </c>
+      <c r="B105" t="s">
+        <v>535</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" t="s">
+        <v>536</v>
+      </c>
+      <c r="E105" t="s">
+        <v>537</v>
+      </c>
+      <c r="F105" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" t="s">
+        <v>538</v>
+      </c>
+      <c r="H105" t="s">
+        <v>539</v>
+      </c>
+      <c r="I105" t="s">
+        <v>275</v>
+      </c>
+      <c r="J105" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105" t="s">
+        <v>73</v>
+      </c>
+      <c r="L105" t="s">
+        <v>540</v>
+      </c>
+      <c r="M105" t="s">
+        <v>541</v>
+      </c>
+      <c r="N105" t="s">
+        <v>542</v>
+      </c>
+      <c r="O105" t="s">
+        <v>327</v>
+      </c>
+      <c r="P105" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>543</v>
+      </c>
+      <c r="B106" t="s">
+        <v>544</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" t="s">
+        <v>401</v>
+      </c>
+      <c r="E106" t="s">
+        <v>402</v>
+      </c>
+      <c r="F106" t="s">
+        <v>15</v>
+      </c>
+      <c r="G106" t="s">
+        <v>403</v>
+      </c>
+      <c r="H106" t="s">
+        <v>404</v>
+      </c>
+      <c r="I106" t="s">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>545</v>
+      </c>
+      <c r="B107" t="s">
+        <v>546</v>
+      </c>
+      <c r="C107" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" t="s">
+        <v>401</v>
+      </c>
+      <c r="E107" t="s">
+        <v>402</v>
+      </c>
+      <c r="F107" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s">
+        <v>403</v>
+      </c>
+      <c r="H107" t="s">
+        <v>404</v>
+      </c>
+      <c r="I107" t="s">
+        <v>83</v>
+      </c>
+      <c r="J107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>548</v>
+      </c>
+      <c r="B108" t="s">
+        <v>549</v>
+      </c>
+      <c r="C108" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" t="s">
+        <v>401</v>
+      </c>
+      <c r="E108" t="s">
+        <v>402</v>
+      </c>
+      <c r="F108" t="s">
+        <v>99</v>
+      </c>
+      <c r="G108" t="s">
+        <v>403</v>
+      </c>
+      <c r="H108" t="s">
+        <v>404</v>
+      </c>
+      <c r="I108" t="s">
+        <v>83</v>
+      </c>
+      <c r="J108" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>550</v>
+      </c>
+      <c r="B109" t="s">
+        <v>551</v>
+      </c>
+      <c r="C109" t="s">
+        <v>120</v>
+      </c>
+      <c r="D109" t="s">
+        <v>401</v>
+      </c>
+      <c r="E109" t="s">
+        <v>402</v>
+      </c>
+      <c r="F109" t="s">
+        <v>15</v>
+      </c>
+      <c r="G109" t="s">
+        <v>528</v>
+      </c>
+      <c r="H109" t="s">
+        <v>529</v>
+      </c>
+      <c r="I109" t="s">
+        <v>25</v>
+      </c>
+      <c r="J109" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>553</v>
+      </c>
+      <c r="B110" t="s">
+        <v>554</v>
+      </c>
+      <c r="C110" t="s">
+        <v>120</v>
+      </c>
+      <c r="D110" t="s">
+        <v>401</v>
+      </c>
+      <c r="E110" t="s">
+        <v>402</v>
+      </c>
+      <c r="F110" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s">
+        <v>447</v>
+      </c>
+      <c r="H110" t="s">
+        <v>448</v>
+      </c>
+      <c r="I110" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>555</v>
+      </c>
+      <c r="B111" t="s">
+        <v>556</v>
+      </c>
+      <c r="C111" t="s">
+        <v>120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>401</v>
+      </c>
+      <c r="E111" t="s">
+        <v>402</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>447</v>
+      </c>
+      <c r="H111" t="s">
+        <v>448</v>
+      </c>
+      <c r="I111" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>558</v>
+      </c>
+      <c r="B112" t="s">
+        <v>559</v>
+      </c>
+      <c r="C112" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" t="s">
+        <v>401</v>
+      </c>
+      <c r="E112" t="s">
+        <v>402</v>
+      </c>
+      <c r="F112" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s">
+        <v>413</v>
+      </c>
+      <c r="H112" t="s">
+        <v>414</v>
+      </c>
+      <c r="I112" t="s">
+        <v>83</v>
+      </c>
+      <c r="J112" t="s">
+        <v>26</v>
+      </c>
+      <c r="M112" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>560</v>
+      </c>
+      <c r="B113" t="s">
+        <v>561</v>
+      </c>
+      <c r="C113" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" t="s">
+        <v>401</v>
+      </c>
+      <c r="E113" t="s">
+        <v>402</v>
+      </c>
+      <c r="F113" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>217</v>
+      </c>
+      <c r="H113" t="s">
+        <v>218</v>
+      </c>
+      <c r="I113" t="s">
+        <v>170</v>
+      </c>
+      <c r="J113" t="s">
+        <v>19</v>
+      </c>
+      <c r="M113" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>563</v>
+      </c>
+      <c r="B114" t="s">
+        <v>564</v>
+      </c>
+      <c r="C114" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" t="s">
+        <v>401</v>
+      </c>
+      <c r="E114" t="s">
+        <v>402</v>
+      </c>
+      <c r="F114" t="s">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>447</v>
+      </c>
+      <c r="H114" t="s">
+        <v>448</v>
+      </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" t="s">
+        <v>26</v>
+      </c>
+      <c r="M114" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>565</v>
+      </c>
+      <c r="B115" t="s">
+        <v>566</v>
+      </c>
+      <c r="C115" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" t="s">
+        <v>401</v>
+      </c>
+      <c r="E115" t="s">
+        <v>402</v>
+      </c>
+      <c r="F115" t="s">
+        <v>99</v>
+      </c>
+      <c r="G115" t="s">
+        <v>567</v>
+      </c>
+      <c r="H115" t="s">
+        <v>568</v>
+      </c>
+      <c r="I115" t="s">
+        <v>109</v>
+      </c>
+      <c r="J115" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>399</v>
+      </c>
+      <c r="B116" t="s">
+        <v>400</v>
+      </c>
+      <c r="C116" t="s">
+        <v>120</v>
+      </c>
+      <c r="D116" t="s">
+        <v>401</v>
+      </c>
+      <c r="E116" t="s">
+        <v>402</v>
+      </c>
+      <c r="F116" t="s">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>403</v>
+      </c>
+      <c r="H116" t="s">
+        <v>404</v>
+      </c>
+      <c r="I116" t="s">
+        <v>83</v>
+      </c>
+      <c r="J116" t="s">
+        <v>26</v>
+      </c>
+      <c r="M116" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>570</v>
+      </c>
+      <c r="B117" t="s">
+        <v>571</v>
+      </c>
+      <c r="C117" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" t="s">
+        <v>401</v>
+      </c>
+      <c r="E117" t="s">
+        <v>402</v>
+      </c>
+      <c r="F117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>403</v>
+      </c>
+      <c r="H117" t="s">
+        <v>404</v>
+      </c>
+      <c r="I117" t="s">
+        <v>83</v>
+      </c>
+      <c r="J117" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>572</v>
+      </c>
+      <c r="B118" t="s">
+        <v>573</v>
+      </c>
+      <c r="C118" t="s">
+        <v>120</v>
+      </c>
+      <c r="D118" t="s">
+        <v>401</v>
+      </c>
+      <c r="E118" t="s">
+        <v>402</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>574</v>
+      </c>
+      <c r="H118" t="s">
+        <v>575</v>
+      </c>
+      <c r="I118" t="s">
+        <v>185</v>
+      </c>
+      <c r="J118" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>577</v>
+      </c>
+      <c r="B119" t="s">
+        <v>578</v>
+      </c>
+      <c r="C119" t="s">
+        <v>120</v>
+      </c>
+      <c r="D119" t="s">
+        <v>401</v>
+      </c>
+      <c r="E119" t="s">
+        <v>402</v>
+      </c>
+      <c r="F119" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>447</v>
+      </c>
+      <c r="H119" t="s">
+        <v>448</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>579</v>
+      </c>
+      <c r="B120" t="s">
+        <v>580</v>
+      </c>
+      <c r="C120" t="s">
+        <v>120</v>
+      </c>
+      <c r="D120" t="s">
+        <v>401</v>
+      </c>
+      <c r="E120" t="s">
+        <v>402</v>
+      </c>
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>413</v>
+      </c>
+      <c r="H120" t="s">
+        <v>414</v>
+      </c>
+      <c r="I120" t="s">
+        <v>83</v>
+      </c>
+      <c r="J120" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" t="s">
+        <v>405</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>